--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487980_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487980_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9633</v>
+        <v>3.7366</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5957</v>
+        <v>6.5376</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.6325</v>
+        <v>-2.8009</v>
       </c>
       <c r="G2" t="n">
         <v>2.5309</v>
@@ -610,13 +610,13 @@
         <v>1.9822</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7782</v>
+        <v>0.5516</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4575</v>
+        <v>0.3994</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3207</v>
+        <v>0.1522</v>
       </c>
       <c r="V2" t="n">
         <v>-0.337</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.467</v>
+        <v>1.5366</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0478</v>
+        <v>0.2184</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5147</v>
+        <v>1.3182</v>
       </c>
       <c r="G3" t="n">
         <v>1.5785</v>
@@ -688,13 +688,13 @@
         <v>1.1893</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1641</v>
+        <v>-0.0945</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8625</v>
+        <v>-0.5964</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6984</v>
+        <v>0.5019</v>
       </c>
       <c r="V3" t="n">
         <v>-1.1367</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.291</v>
+        <v>1.2629</v>
       </c>
       <c r="E4" t="n">
         <v>1.7352</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4442</v>
+        <v>-0.4723</v>
       </c>
       <c r="G4" t="n">
         <v>1.3157</v>
@@ -766,13 +766,13 @@
         <v>0.3964</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1545</v>
+        <v>-0.1826</v>
       </c>
       <c r="T4" t="n">
         <v>-0.1762</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0216</v>
+        <v>-0.0065</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2666</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5767</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2568</v>
+        <v>2.2403</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6802</v>
+        <v>-1.6521</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2234</v>
@@ -844,13 +844,13 @@
         <v>3.9645</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.407</v>
+        <v>-0.3955</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3447</v>
+        <v>-0.3613</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0623</v>
+        <v>-0.0342</v>
       </c>
       <c r="V5" t="n">
         <v>1.2071</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8847</v>
+        <v>-0.341</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.5882</v>
+        <v>-3.0164</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7035</v>
+        <v>2.6754</v>
       </c>
       <c r="G7" t="n">
         <v>-0.537</v>
@@ -1000,13 +1000,13 @@
         <v>2.1805</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2793</v>
+        <v>0.2643</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7157</v>
+        <v>-0.1439</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4363</v>
+        <v>0.4083</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2666</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0953</v>
+        <v>-0.7501</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2336</v>
+        <v>-0.9445</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1383</v>
+        <v>0.1944</v>
       </c>
       <c r="G8" t="n">
         <v>-1.35</v>
@@ -1078,13 +1078,13 @@
         <v>1.1893</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.005</v>
+        <v>-0.6598000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6753</v>
+        <v>-0.3863</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3297</v>
+        <v>-0.2735</v>
       </c>
       <c r="V8" t="n">
         <v>0.0704</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0929</v>
+        <v>-1.911</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7969</v>
+        <v>-1.5308</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.296</v>
+        <v>-0.3802</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0881</v>
@@ -1156,13 +1156,13 @@
         <v>0.7929</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.203</v>
+        <v>-0.0211</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1872</v>
+        <v>0.0789</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0158</v>
+        <v>-0.1001</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6036</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1889</v>
+        <v>-2.5235</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.6148</v>
+        <v>-5.0618</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4259</v>
+        <v>2.5383</v>
       </c>
       <c r="G10" t="n">
         <v>-3.4288</v>
@@ -1234,13 +1234,13 @@
         <v>2.1805</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9009</v>
+        <v>0.5662</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8187</v>
+        <v>0.3718</v>
       </c>
       <c r="U10" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.1944</v>
       </c>
       <c r="V10" t="n">
         <v>0.1408</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5169</v>
+        <v>-3.9004</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5984</v>
+        <v>1.1306</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.1152</v>
+        <v>-5.031</v>
       </c>
       <c r="G11" t="n">
         <v>-2.3065</v>
@@ -1312,13 +1312,13 @@
         <v>1.9822</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7367</v>
+        <v>-0.1202</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7781</v>
+        <v>-0.2458</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0413</v>
+        <v>0.1256</v>
       </c>
       <c r="V11" t="n">
         <v>-1.4737</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6179</v>
+        <v>-4.2561</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.0159</v>
+        <v>-4.7103</v>
       </c>
       <c r="F12" t="n">
-        <v>0.398</v>
+        <v>0.4542</v>
       </c>
       <c r="G12" t="n">
         <v>0.0333</v>
@@ -1390,13 +1390,13 @@
         <v>1.5858</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8692</v>
+        <v>-0.5075</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8001</v>
+        <v>-0.4945</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.06909999999999999</v>
+        <v>-0.0129</v>
       </c>
       <c r="V12" t="n">
         <v>-1.4033</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. GARCIA MONTELLANO</t>
+          <t>P. BILEISIS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.2909</v>
+        <v>-4.9809</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.4011</v>
+        <v>-2.0431</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.8897</v>
+        <v>-2.9378</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.173</v>
+        <v>-4.8145</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3248</v>
+        <v>3.1231</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.4978</v>
+        <v>-7.9375</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5553</v>
+        <v>-1.5596</v>
       </c>
       <c r="K13" t="n">
-        <v>2.3879</v>
+        <v>3.7127</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.8326</v>
+        <v>-5.2723</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.7283</v>
+        <v>-3.2548</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.0631</v>
+        <v>-0.5896</v>
       </c>
       <c r="O13" t="n">
         <v>-2.6652</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.3964</v>
+        <v>1.784</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5858</v>
+        <v>1.784</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0893</v>
+        <v>-0.7433</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0259</v>
+        <v>-0.4835</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0634</v>
+        <v>-0.2598</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.8107</v>
+        <v>-1.2071</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.8107</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. BILEISIS</t>
+          <t>A. GARCIA MONTELLANO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.3708</v>
+        <v>-5.2856</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.3487</v>
+        <v>-1.4801</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.022</v>
+        <v>-3.8055</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.8145</v>
+        <v>-3.173</v>
       </c>
       <c r="H14" t="n">
-        <v>3.1231</v>
+        <v>1.3248</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.9375</v>
+        <v>-4.4978</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.5596</v>
+        <v>0.5553</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7127</v>
+        <v>2.3879</v>
       </c>
       <c r="L14" t="n">
-        <v>-5.2723</v>
+        <v>-1.8326</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.2548</v>
+        <v>-3.7283</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5896</v>
+        <v>-1.0631</v>
       </c>
       <c r="O14" t="n">
         <v>-2.6652</v>
       </c>
       <c r="P14" t="n">
-        <v>1.784</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R14" t="n">
-        <v>1.784</v>
+        <v>1.5858</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1332</v>
+        <v>0.0945</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7891</v>
+        <v>-0.0531</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3441</v>
+        <v>0.1476</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2071</v>
+        <v>-1.8107</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2071</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-17.4576</v>
+        <v>-16.5216</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.5582</v>
+        <v>-6.622199999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-9.8994</v>
+        <v>-9.8993</v>
       </c>
       <c r="G15" t="n">
         <v>-11.1602</v>
@@ -1603,13 +1603,13 @@
         <v>15.3453</v>
       </c>
       <c r="L15" t="n">
-        <v>-6.9908</v>
+        <v>-6.990800000000001</v>
       </c>
       <c r="M15" t="n">
         <v>-19.5147</v>
       </c>
       <c r="N15" t="n">
-        <v>-8.962200000000001</v>
+        <v>-8.962199999999999</v>
       </c>
       <c r="O15" t="n">
         <v>-10.5524</v>
@@ -1624,16 +1624,16 @@
         <v>20.8134</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.1836</v>
+        <v>-1.2479</v>
       </c>
       <c r="T15" t="n">
-        <v>-3.0268</v>
+        <v>-2.0909</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8428</v>
+        <v>0.843</v>
       </c>
       <c r="V15" t="n">
-        <v>-7.087</v>
+        <v>-7.086999999999999</v>
       </c>
       <c r="W15" t="n">
         <v>4.9542</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>13.6204</v>
+        <v>13.0562</v>
       </c>
       <c r="E16" t="n">
-        <v>12.9669</v>
+        <v>12.3557</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6535</v>
+        <v>0.7005</v>
       </c>
       <c r="G16" t="n">
         <v>7.354</v>
@@ -1702,13 +1702,13 @@
         <v>1.9822</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2069</v>
+        <v>1.6427</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4244</v>
+        <v>0.8132</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7824</v>
+        <v>0.8294</v>
       </c>
       <c r="V16" t="n">
         <v>2.0772</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3925</v>
+        <v>4.3107</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6264</v>
+        <v>1.0339</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7661</v>
+        <v>3.2768</v>
       </c>
       <c r="G17" t="n">
         <v>0.3134</v>
@@ -1780,13 +1780,13 @@
         <v>1.9822</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3767</v>
+        <v>0.5414</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1745</v>
+        <v>-0.767</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7978</v>
+        <v>1.3084</v>
       </c>
       <c r="V17" t="n">
         <v>1.4737</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. VICENTE BOSCH</t>
+          <t>M. GAMEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.2258</v>
+        <v>3.1209</v>
       </c>
       <c r="E18" t="n">
-        <v>4.3102</v>
+        <v>2.4792</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0844</v>
+        <v>0.6417</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2107</v>
+        <v>0.6942</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2165</v>
+        <v>-1.4907</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4272</v>
+        <v>2.1849</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9978</v>
+        <v>2.0777</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5877</v>
+        <v>0.1816</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4101</v>
+        <v>1.8961</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7871</v>
+        <v>-1.3836</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.8042</v>
+        <v>-1.6723</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0171</v>
+        <v>0.2888</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1982</v>
+        <v>0.7929</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R18" t="n">
         <v>1.784</v>
       </c>
       <c r="S18" t="n">
-        <v>2.3542</v>
+        <v>0.4267</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2284</v>
+        <v>0.1855</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1258</v>
+        <v>0.2412</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1408</v>
+        <v>1.2071</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0663</v>
+        <v>1.2071</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. GAMEZ SANCHEZ</t>
+          <t>J. VICENTE BOSCH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.5939</v>
+        <v>2.0876</v>
       </c>
       <c r="E19" t="n">
-        <v>1.868</v>
+        <v>3.0878</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7259</v>
+        <v>-1.0002</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6942</v>
+        <v>1.2107</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4907</v>
+        <v>-0.2165</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1849</v>
+        <v>1.4272</v>
       </c>
       <c r="J19" t="n">
-        <v>2.0777</v>
+        <v>2.9978</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1816</v>
+        <v>1.5877</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8961</v>
+        <v>1.4101</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3836</v>
+        <v>-1.7871</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6723</v>
+        <v>-1.8042</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2888</v>
+        <v>0.0171</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7929</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R19" t="n">
         <v>1.784</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1003</v>
+        <v>1.216</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4257</v>
+        <v>1.0059</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3255</v>
+        <v>0.21</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2071</v>
+        <v>-0.1408</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2071</v>
+        <v>1.0663</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. CERISUELO QUESADA</t>
+          <t>D. MALAVE FERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.332</v>
+        <v>0.6939</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5169</v>
+        <v>-0.8807</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8489</v>
+        <v>1.5746</v>
       </c>
       <c r="G20" t="n">
-        <v>2.5735</v>
+        <v>0.3086</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1541</v>
+        <v>0.0024</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4194</v>
+        <v>0.3061</v>
       </c>
       <c r="J20" t="n">
-        <v>2.6066</v>
+        <v>0.5531</v>
       </c>
       <c r="K20" t="n">
-        <v>1.8834</v>
+        <v>0.6659</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7232</v>
+        <v>-0.1128</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0331</v>
+        <v>-0.2446</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7294</v>
+        <v>-0.6634</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6962</v>
+        <v>0.4189</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5858</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9733</v>
+        <v>-0.9911</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3876</v>
+        <v>0.9911</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3552</v>
+        <v>-0.5552</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6129</v>
+        <v>-0.7093</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.1541</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0109</v>
+        <v>0.9405</v>
       </c>
       <c r="W20" t="n">
-        <v>0.4627</v>
+        <v>0.2666</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4737</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. CURBELO MENENDEZ</t>
+          <t>J. CERISUELO QUESADA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.038</v>
+        <v>0.6062</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1277</v>
+        <v>-0.3132</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0896</v>
+        <v>0.9194</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8875</v>
+        <v>2.5735</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6889999999999999</v>
+        <v>1.1541</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5765</v>
+        <v>1.4194</v>
       </c>
       <c r="J21" t="n">
-        <v>2.3427</v>
+        <v>2.6066</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0492</v>
+        <v>1.8834</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2935</v>
+        <v>0.7232</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4552</v>
+        <v>-0.0331</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.7383</v>
+        <v>-0.7294</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2831</v>
+        <v>0.6962</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3964</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9822</v>
+        <v>-2.9733</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5858</v>
+        <v>1.3876</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2625</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4881</v>
+        <v>-0.4092</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2256</v>
+        <v>1.0387</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2666</v>
+        <v>-1.0109</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.4627</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2666</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. MALAVE FERNANDEZ</t>
+          <t>S. CURBELO MENENDEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1524</v>
+        <v>0.5346</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9826</v>
+        <v>0.5854</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8302</v>
+        <v>-0.0508</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3086</v>
+        <v>0.8875</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0024</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3061</v>
+        <v>1.5765</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5531</v>
+        <v>2.3427</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6659</v>
+        <v>1.0492</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1128</v>
+        <v>1.2935</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2446</v>
+        <v>-1.4552</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6634</v>
+        <v>-1.7383</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4189</v>
+        <v>0.2831</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9911</v>
+        <v>1.5858</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4015</v>
+        <v>0.3102</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8112</v>
+        <v>0.2249</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5903</v>
+        <v>0.0852</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9405</v>
+        <v>-0.2666</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.674</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4334</v>
+        <v>-1.4497</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8612</v>
+        <v>-3.0649</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4277</v>
+        <v>1.6151</v>
       </c>
       <c r="G23" t="n">
         <v>-3.2423</v>
@@ -2248,13 +2248,13 @@
         <v>2.3787</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6633</v>
+        <v>0.647</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1948</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4685</v>
+        <v>0.6559</v>
       </c>
       <c r="V23" t="n">
         <v>1.7403</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.7197</v>
+        <v>-4.6342</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.6101</v>
+        <v>-5.1194</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1096</v>
+        <v>0.4853</v>
       </c>
       <c r="G24" t="n">
         <v>0.6133</v>
@@ -2326,13 +2326,13 @@
         <v>1.9822</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5385</v>
+        <v>0.6241</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0589</v>
+        <v>-0.4504</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4796</v>
+        <v>1.0745</v>
       </c>
       <c r="V24" t="n">
         <v>1.0663</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>16.8211</v>
+        <v>18.3262</v>
       </c>
       <c r="E25" t="n">
-        <v>10.673</v>
+        <v>10.1638</v>
       </c>
       <c r="F25" t="n">
-        <v>6.1479</v>
+        <v>8.1624</v>
       </c>
       <c r="G25" t="n">
         <v>10.7129</v>
@@ -2386,7 +2386,7 @@
         <v>10.3516</v>
       </c>
       <c r="M25" t="n">
-        <v>-8.338900000000001</v>
+        <v>-8.338899999999999</v>
       </c>
       <c r="N25" t="n">
         <v>-13.9485</v>
@@ -2404,13 +2404,13 @@
         <v>15.8578</v>
       </c>
       <c r="S25" t="n">
-        <v>3.9771</v>
+        <v>5.4824</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3941</v>
+        <v>-0.1154000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>3.5831</v>
+        <v>5.5974</v>
       </c>
       <c r="V25" t="n">
         <v>7.0868</v>
